--- a/paper/workspace/TruongDT/outputs/AI_AuditLog_TruongDT_M05B.xlsx
+++ b/paper/workspace/TruongDT/outputs/AI_AuditLog_TruongDT_M05B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\Pictures\TruongDT\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231D5B4D-0E14-4A2A-B260-E20F2DD2CE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF958A3-E5C5-40EF-B702-88C67178CE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Student Name:</t>
   </si>
   <si>
-    <t>TruongDT</t>
-  </si>
-  <si>
     <t>Student ID:</t>
   </si>
   <si>
@@ -404,6 +401,9 @@
   </si>
   <si>
     <t xml:space="preserve">HALLUCINATION DETECTION LOG </t>
+  </si>
+  <si>
+    <t>Phan Huu Nhat Truong</t>
   </si>
 </sst>
 </file>
@@ -754,7 +754,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -767,178 +767,178 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>21</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
         <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -963,142 +963,142 @@
   <sheetData>
     <row r="1" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>45</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>46</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
         <v>114</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
         <v>54</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>56</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>58</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>59</v>
-      </c>
-      <c r="H5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>63</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>65</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>66</v>
-      </c>
-      <c r="H6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>69</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>70</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="G7" t="s">
-        <v>72</v>
-      </c>
       <c r="H7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1121,52 +1121,52 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>76</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>78</v>
-      </c>
-      <c r="F3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
         <v>80</v>
       </c>
-      <c r="C4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>81</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>82</v>
-      </c>
-      <c r="F4" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1187,190 +1187,190 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>87</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" t="s">
         <v>93</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
         <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s">
         <v>96</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
         <v>97</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
         <v>99</v>
-      </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" t="s">
         <v>101</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
         <v>102</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
         <v>86</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
         <v>107</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
         <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
         <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
